--- a/Assets/_TankRes/excel/stage.xlsx
+++ b/Assets/_TankRes/excel/stage.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="stage" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="44">
   <si>
     <t>关卡唯一标识</t>
   </si>
@@ -69,6 +69,96 @@
   </si>
   <si>
     <t>{201,0.1},{202,0.1},{203,0.1},{204,0.1},{205,0.1},{301,0.2},{302,0.2},{303,0.1}</t>
+  </si>
+  <si>
+    <t>{201,0.1},{202,0.1},{203,0.1},{204,0.1},{205,0.1},{301,0.2},{302,0.2},{303,0.2}</t>
+  </si>
+  <si>
+    <t>{201,0.1},{202,0.1},{203,0.1},{204,0.1},{205,0.1},{301,0.2},{302,0.2},{303,0.3}</t>
+  </si>
+  <si>
+    <t>{201,0.1},{202,0.1},{203,0.1},{204,0.1},{205,0.1},{301,0.2},{302,0.2},{303,0.4}</t>
+  </si>
+  <si>
+    <t>{201,0.1},{202,0.1},{203,0.1},{204,0.1},{205,0.1},{301,0.2},{302,0.2},{303,0.5}</t>
+  </si>
+  <si>
+    <t>{201,0.1},{202,0.1},{203,0.1},{204,0.1},{205,0.1},{301,0.2},{302,0.2},{303,0.6}</t>
+  </si>
+  <si>
+    <t>{201,0.1},{202,0.1},{203,0.1},{204,0.1},{205,0.1},{301,0.2},{302,0.2},{303,0.7}</t>
+  </si>
+  <si>
+    <t>{201,0.1},{202,0.1},{203,0.1},{204,0.1},{205,0.1},{301,0.2},{302,0.2},{303,0.8}</t>
+  </si>
+  <si>
+    <t>{201,0.1},{202,0.1},{203,0.1},{204,0.1},{205,0.1},{301,0.2},{302,0.2},{303,0.9}</t>
+  </si>
+  <si>
+    <t>{201,0.1},{202,0.1},{203,0.1},{204,0.1},{205,0.1},{301,0.2},{302,0.2},{303,0.10}</t>
+  </si>
+  <si>
+    <t>{201,0.1},{202,0.1},{203,0.1},{204,0.1},{205,0.1},{301,0.2},{302,0.2},{303,0.11}</t>
+  </si>
+  <si>
+    <t>{201,0.1},{202,0.1},{203,0.1},{204,0.1},{205,0.1},{301,0.2},{302,0.2},{303,0.12}</t>
+  </si>
+  <si>
+    <t>{201,0.1},{202,0.1},{203,0.1},{204,0.1},{205,0.1},{301,0.2},{302,0.2},{303,0.13}</t>
+  </si>
+  <si>
+    <t>{201,0.1},{202,0.1},{203,0.1},{204,0.1},{205,0.1},{301,0.2},{302,0.2},{303,0.14}</t>
+  </si>
+  <si>
+    <t>{201,0.1},{202,0.1},{203,0.1},{204,0.1},{205,0.1},{301,0.2},{302,0.2},{303,0.15}</t>
+  </si>
+  <si>
+    <t>{201,0.1},{202,0.1},{203,0.1},{204,0.1},{205,0.1},{301,0.2},{302,0.2},{303,0.16}</t>
+  </si>
+  <si>
+    <t>{201,0.1},{202,0.1},{203,0.1},{204,0.1},{205,0.1},{301,0.2},{302,0.2},{303,0.17}</t>
+  </si>
+  <si>
+    <t>{201,0.1},{202,0.1},{203,0.1},{204,0.1},{205,0.1},{301,0.2},{302,0.2},{303,0.18}</t>
+  </si>
+  <si>
+    <t>{201,0.1},{202,0.1},{203,0.1},{204,0.1},{205,0.1},{301,0.2},{302,0.2},{303,0.19}</t>
+  </si>
+  <si>
+    <t>{201,0.1},{202,0.1},{203,0.1},{204,0.1},{205,0.1},{301,0.2},{302,0.2},{303,0.20}</t>
+  </si>
+  <si>
+    <t>{201,0.1},{202,0.1},{203,0.1},{204,0.1},{205,0.1},{301,0.2},{302,0.2},{303,0.21}</t>
+  </si>
+  <si>
+    <t>{201,0.1},{202,0.1},{203,0.1},{204,0.1},{205,0.1},{301,0.2},{302,0.2},{303,0.22}</t>
+  </si>
+  <si>
+    <t>{201,0.1},{202,0.1},{203,0.1},{204,0.1},{205,0.1},{301,0.2},{302,0.2},{303,0.23}</t>
+  </si>
+  <si>
+    <t>{201,0.1},{202,0.1},{203,0.1},{204,0.1},{205,0.1},{301,0.2},{302,0.2},{303,0.24}</t>
+  </si>
+  <si>
+    <t>{201,0.1},{202,0.1},{203,0.1},{204,0.1},{205,0.1},{301,0.2},{302,0.2},{303,0.25}</t>
+  </si>
+  <si>
+    <t>{201,0.1},{202,0.1},{203,0.1},{204,0.1},{205,0.1},{301,0.2},{302,0.2},{303,0.26}</t>
+  </si>
+  <si>
+    <t>{201,0.1},{202,0.1},{203,0.1},{204,0.1},{205,0.1},{301,0.2},{302,0.2},{303,0.27}</t>
+  </si>
+  <si>
+    <t>{201,0.1},{202,0.1},{203,0.1},{204,0.1},{205,0.1},{301,0.2},{302,0.2},{303,0.28}</t>
+  </si>
+  <si>
+    <t>{201,0.1},{202,0.1},{203,0.1},{204,0.1},{205,0.1},{301,0.2},{302,0.2},{303,0.29}</t>
+  </si>
+  <si>
+    <t>{201,0.1},{202,0.1},{203,0.1},{204,0.1},{205,0.1},{301,0.2},{302,0.2},{303,0.30}</t>
+  </si>
+  <si>
+    <t>{201,0.1},{202,0.1},{203,0.1},{204,0.1},{205,0.1},{301,0.2},{302,0.2},{303,0.31}</t>
   </si>
 </sst>
 </file>
@@ -1055,7 +1145,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="19.0083333333333" style="1" customWidth="1"/>
@@ -1179,7 +1269,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="5">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>13</v>
@@ -1197,7 +1287,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="5">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>13</v>
@@ -1215,7 +1305,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="5">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>13</v>
@@ -1228,45 +1318,520 @@
       </c>
       <c r="F9" s="3"/>
     </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
+    <row r="10" ht="33.75" spans="1:6">
+      <c r="A10" s="5">
+        <v>6</v>
+      </c>
+      <c r="B10" s="5">
+        <v>20</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="5">
+        <v>120</v>
+      </c>
+      <c r="E10" s="5">
+        <v>1</v>
+      </c>
       <c r="F10" s="3"/>
     </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
+    <row r="11" ht="33.75" spans="1:6">
+      <c r="A11" s="5">
+        <v>7</v>
+      </c>
+      <c r="B11" s="5">
+        <v>20</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="5">
+        <v>120</v>
+      </c>
+      <c r="E11" s="5">
+        <v>1</v>
+      </c>
       <c r="F11" s="3"/>
     </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
+    <row r="12" ht="33.75" spans="1:6">
+      <c r="A12" s="5">
+        <v>8</v>
+      </c>
+      <c r="B12" s="5">
+        <v>20</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="5">
+        <v>120</v>
+      </c>
+      <c r="E12" s="5">
+        <v>1</v>
+      </c>
       <c r="F12" s="3"/>
     </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
+    <row r="13" ht="33.75" spans="1:6">
+      <c r="A13" s="5">
+        <v>9</v>
+      </c>
+      <c r="B13" s="5">
+        <v>20</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="5">
+        <v>120</v>
+      </c>
+      <c r="E13" s="5">
+        <v>1</v>
+      </c>
       <c r="F13" s="3"/>
     </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
+    <row r="14" ht="33.75" spans="1:6">
+      <c r="A14" s="5">
+        <v>10</v>
+      </c>
+      <c r="B14" s="5">
+        <v>20</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="5">
+        <v>120</v>
+      </c>
+      <c r="E14" s="5">
+        <v>1</v>
+      </c>
       <c r="F14" s="3"/>
+    </row>
+    <row r="15" ht="33.75" spans="1:6">
+      <c r="A15" s="5">
+        <v>11</v>
+      </c>
+      <c r="B15" s="5">
+        <v>20</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="5">
+        <v>120</v>
+      </c>
+      <c r="E15" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" ht="33.75" spans="1:6">
+      <c r="A16" s="5">
+        <v>12</v>
+      </c>
+      <c r="B16" s="5">
+        <v>20</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="5">
+        <v>120</v>
+      </c>
+      <c r="E16" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" ht="33.75" spans="1:5">
+      <c r="A17" s="5">
+        <v>13</v>
+      </c>
+      <c r="B17" s="5">
+        <v>20</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" s="5">
+        <v>120</v>
+      </c>
+      <c r="E17" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" ht="33.75" spans="1:5">
+      <c r="A18" s="5">
+        <v>14</v>
+      </c>
+      <c r="B18" s="5">
+        <v>20</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D18" s="5">
+        <v>120</v>
+      </c>
+      <c r="E18" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" ht="33.75" spans="1:5">
+      <c r="A19" s="5">
+        <v>15</v>
+      </c>
+      <c r="B19" s="5">
+        <v>20</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19" s="5">
+        <v>120</v>
+      </c>
+      <c r="E19" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" ht="33.75" spans="1:5">
+      <c r="A20" s="5">
+        <v>16</v>
+      </c>
+      <c r="B20" s="5">
+        <v>25</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D20" s="5">
+        <v>120</v>
+      </c>
+      <c r="E20" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" ht="33.75" spans="1:5">
+      <c r="A21" s="5">
+        <v>17</v>
+      </c>
+      <c r="B21" s="5">
+        <v>25</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D21" s="5">
+        <v>120</v>
+      </c>
+      <c r="E21" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" ht="33.75" spans="1:5">
+      <c r="A22" s="5">
+        <v>18</v>
+      </c>
+      <c r="B22" s="5">
+        <v>25</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D22" s="5">
+        <v>120</v>
+      </c>
+      <c r="E22" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" ht="33.75" spans="1:5">
+      <c r="A23" s="5">
+        <v>19</v>
+      </c>
+      <c r="B23" s="5">
+        <v>25</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D23" s="5">
+        <v>120</v>
+      </c>
+      <c r="E23" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" ht="33.75" spans="1:5">
+      <c r="A24" s="5">
+        <v>20</v>
+      </c>
+      <c r="B24" s="5">
+        <v>25</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D24" s="5">
+        <v>120</v>
+      </c>
+      <c r="E24" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" ht="33.75" spans="1:5">
+      <c r="A25" s="5">
+        <v>21</v>
+      </c>
+      <c r="B25" s="5">
+        <v>25</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D25" s="5">
+        <v>120</v>
+      </c>
+      <c r="E25" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" ht="33.75" spans="1:5">
+      <c r="A26" s="5">
+        <v>22</v>
+      </c>
+      <c r="B26" s="5">
+        <v>25</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D26" s="5">
+        <v>120</v>
+      </c>
+      <c r="E26" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" ht="33.75" spans="1:5">
+      <c r="A27" s="5">
+        <v>23</v>
+      </c>
+      <c r="B27" s="5">
+        <v>25</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D27" s="5">
+        <v>120</v>
+      </c>
+      <c r="E27" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" ht="33.75" spans="1:5">
+      <c r="A28" s="5">
+        <v>24</v>
+      </c>
+      <c r="B28" s="5">
+        <v>25</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D28" s="5">
+        <v>120</v>
+      </c>
+      <c r="E28" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" ht="33.75" spans="1:5">
+      <c r="A29" s="5">
+        <v>25</v>
+      </c>
+      <c r="B29" s="5">
+        <v>25</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D29" s="5">
+        <v>120</v>
+      </c>
+      <c r="E29" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" ht="33.75" spans="1:5">
+      <c r="A30" s="5">
+        <v>26</v>
+      </c>
+      <c r="B30" s="5">
+        <v>30</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D30" s="5">
+        <v>120</v>
+      </c>
+      <c r="E30" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" ht="33.75" spans="1:5">
+      <c r="A31" s="5">
+        <v>27</v>
+      </c>
+      <c r="B31" s="5">
+        <v>31</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D31" s="5">
+        <v>120</v>
+      </c>
+      <c r="E31" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" ht="33.75" spans="1:5">
+      <c r="A32" s="5">
+        <v>28</v>
+      </c>
+      <c r="B32" s="5">
+        <v>32</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D32" s="5">
+        <v>120</v>
+      </c>
+      <c r="E32" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" ht="33.75" spans="1:5">
+      <c r="A33" s="5">
+        <v>29</v>
+      </c>
+      <c r="B33" s="5">
+        <v>33</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D33" s="5">
+        <v>120</v>
+      </c>
+      <c r="E33" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" ht="33.75" spans="1:5">
+      <c r="A34" s="5">
+        <v>30</v>
+      </c>
+      <c r="B34" s="5">
+        <v>34</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D34" s="5">
+        <v>120</v>
+      </c>
+      <c r="E34" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" ht="33.75" spans="1:5">
+      <c r="A35" s="5">
+        <v>31</v>
+      </c>
+      <c r="B35" s="5">
+        <v>35</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D35" s="5">
+        <v>120</v>
+      </c>
+      <c r="E35" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" ht="33.75" spans="1:5">
+      <c r="A36" s="5">
+        <v>32</v>
+      </c>
+      <c r="B36" s="5">
+        <v>36</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D36" s="5">
+        <v>120</v>
+      </c>
+      <c r="E36" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" ht="33.75" spans="1:5">
+      <c r="A37" s="5">
+        <v>33</v>
+      </c>
+      <c r="B37" s="5">
+        <v>37</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D37" s="5">
+        <v>120</v>
+      </c>
+      <c r="E37" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" ht="33.75" spans="1:5">
+      <c r="A38" s="5">
+        <v>34</v>
+      </c>
+      <c r="B38" s="5">
+        <v>38</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D38" s="5">
+        <v>120</v>
+      </c>
+      <c r="E38" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" ht="33.75" spans="1:5">
+      <c r="A39" s="5">
+        <v>35</v>
+      </c>
+      <c r="B39" s="5">
+        <v>39</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D39" s="5">
+        <v>120</v>
+      </c>
+      <c r="E39" s="5">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
